--- a/data/trans_camb/IP11A_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP11A_R-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,22 +624,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,96</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,96</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 30,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,8</t>
+          <t>0,0; 16,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -730,22 +730,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -840,34 +840,34 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,81</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-3,03</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,06</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,84</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-3,03</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,53</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,21</t>
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>5,17</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,68</t>
+          <t>-10,33; 4,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-16,75; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,15; 47,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 4,49</t>
+          <t>0,0; 15,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 50,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 5,76</t>
+          <t>-3,68; 5,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 0,0</t>
+          <t>-10,26; 0,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 29,57</t>
+          <t>-3,29; 28,52</t>
         </is>
       </c>
     </row>
@@ -946,47 +946,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-26,66%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>298,56%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-26,66%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>72,97%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>314,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>72,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>354,5%</t>
+          <t>312,18%</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10,05</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13,14</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>20,07</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>15,46</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10,05</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,14</t>
+          <t>13,99</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14,04</t>
+          <t>13,48</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 42,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,35</t>
+          <t>0,0; 55,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 62,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,26</t>
+          <t>0,0; 54,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,51</t>
+          <t>0,0; 22,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,38</t>
+          <t>0,0; 21,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,34</t>
+          <t>0,0; 41,76</t>
         </is>
       </c>
     </row>
@@ -1162,27 +1162,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-10,82</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-10,82</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>15,49</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7,56</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-10,82</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,8</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-10,82</t>
+          <t>7,34</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,67</t>
+          <t>-2,59</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-32,47; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,59</t>
+          <t>-22,56; 13,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,54</t>
+          <t>-32,62; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-32,24; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-21,99; 16,4</t>
+          <t>0,0; 39,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-33,91; 0,0</t>
+          <t>0,0; 35,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 0,0</t>
+          <t>-20,81; 0,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 20,06</t>
+          <t>-6,82; 20,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 7,46</t>
+          <t>-12,13; 9,75</t>
         </is>
       </c>
     </row>
@@ -1378,39 +1378,39 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-16,6%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-16,6%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>90,81%</t>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-43,8%</t>
+          <t>-42,46%</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,49</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,73</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3,07</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>1,37</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>11,77</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>7,83</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,19</t>
+          <t>7,45</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>4,97</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,19</t>
+          <t>-6,08; 5,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,27; 26,87</t>
+          <t>-6,41; 6,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,91</t>
+          <t>-4,26; 21,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 5,32</t>
+          <t>0,0; 6,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 6,6</t>
+          <t>3,33; 26,61</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 20,77</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 4,02</t>
+          <t>-3,19; 4,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 10,27</t>
+          <t>-0,57; 10,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 15,73</t>
+          <t>-0,78; 14,75</t>
         </is>
       </c>
     </row>
@@ -1594,34 +1594,34 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-12,46%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-18,59%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>78,3%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-12,46%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-18,59%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>81,35%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
           <t>15,74%</t>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>232,36%</t>
+          <t>222,53%</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-45,16; —</t>
+          <t>-51,15; 2258,29</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
